--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484062_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484062_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6354</v>
+        <v>5.2</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6546</v>
+        <v>3.3314</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9808</v>
+        <v>1.8686</v>
       </c>
       <c r="G2" t="n">
         <v>4.9786</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1292</v>
+        <v>-0.3062</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9353</v>
+        <v>0.6122</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8062</v>
+        <v>-0.9184</v>
       </c>
       <c r="V2" t="n">
         <v>-0.266</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8994</v>
+        <v>3.0459</v>
       </c>
       <c r="E3" t="n">
-        <v>2.482</v>
+        <v>2.5444</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4173</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>2.2575</v>
@@ -688,13 +688,13 @@
         <v>0.5952</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6241</v>
+        <v>-0.4776</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1304</v>
+        <v>0.1928</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.6704</v>
       </c>
       <c r="V3" t="n">
         <v>0.8692</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. BAQUES GARCIA</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3916</v>
+        <v>2.6773</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0085</v>
+        <v>1.74</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3832</v>
+        <v>0.9372</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1662</v>
+        <v>3.7136</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.2844</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3905</v>
+        <v>2.4292</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6898</v>
+        <v>3.0421</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4743</v>
+        <v>0.5093</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2155</v>
+        <v>2.5327</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4764</v>
+        <v>0.6715</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3014</v>
+        <v>0.7751</v>
       </c>
       <c r="O4" t="n">
-        <v>0.175</v>
+        <v>-0.1035</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3887</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.5709</v>
+        <v>-3.3725</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1822</v>
+        <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6519</v>
+        <v>-0.727</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6236</v>
+        <v>0.2608</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2755</v>
+        <v>-0.9878</v>
       </c>
       <c r="V4" t="n">
-        <v>0.266</v>
+        <v>1.2777</v>
       </c>
       <c r="W4" t="n">
-        <v>0.266</v>
+        <v>1.8097</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>N. BAQUES GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6817</v>
+        <v>2.1705</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9408</v>
+        <v>0.7874</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7408</v>
+        <v>1.3832</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7136</v>
+        <v>4.1662</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2844</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4292</v>
+        <v>3.3905</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0421</v>
+        <v>3.6898</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5093</v>
+        <v>0.4743</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5327</v>
+        <v>3.2155</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6715</v>
+        <v>0.4764</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7751</v>
+        <v>0.3014</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1035</v>
+        <v>0.175</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5871</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.3725</v>
+        <v>-3.5709</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7855</v>
+        <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7226</v>
+        <v>-0.873</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5384</v>
+        <v>0.4025</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1842</v>
+        <v>-1.2755</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2777</v>
+        <v>0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8097</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>B. CANOVAS PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3877</v>
+        <v>0.1828</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5818</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1941</v>
+        <v>0.1828</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5833</v>
+        <v>0.136</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1185</v>
+        <v>0.136</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5351</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6701</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7906</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1205</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0867</v>
+        <v>0.136</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3279</v>
+        <v>0.136</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4146</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3678</v>
+        <v>0.0468</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2438</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1241</v>
+        <v>0.0468</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. CANOVAS PEREZ</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1547</v>
+        <v>-0.1148</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.2757</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1547</v>
+        <v>-0.3904</v>
       </c>
       <c r="G7" t="n">
-        <v>0.136</v>
+        <v>-0.5833</v>
       </c>
       <c r="H7" t="n">
-        <v>0.136</v>
+        <v>-1.1185</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5351</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.6701</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.7906</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1205</v>
       </c>
       <c r="M7" t="n">
-        <v>0.136</v>
+        <v>0.0867</v>
       </c>
       <c r="N7" t="n">
-        <v>0.136</v>
+        <v>-0.3279</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.4146</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0187</v>
+        <v>-0.1346</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.0623</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0187</v>
+        <v>-0.0723</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08939999999999999</v>
+        <v>-0.4284</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4143</v>
+        <v>-0.2999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3249</v>
+        <v>-0.1285</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0902</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.378</v>
+        <v>0.8602</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3831</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0051</v>
+        <v>0.1913</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8837</v>
+        <v>-0.4708</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1155</v>
+        <v>0.4442</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9992</v>
+        <v>-0.915</v>
       </c>
       <c r="G9" t="n">
         <v>2.6987</v>
@@ -1156,13 +1156,13 @@
         <v>1.7855</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2533</v>
+        <v>-0.8404</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4988</v>
+        <v>-0.17</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.6704</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9405</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0141</v>
+        <v>-0.5142</v>
       </c>
       <c r="E10" t="n">
-        <v>0.676</v>
+        <v>1.2882</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6901</v>
+        <v>-1.8023</v>
       </c>
       <c r="G10" t="n">
         <v>3.8713</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4887</v>
+        <v>0.0113</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1643</v>
+        <v>0.4478</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3243</v>
+        <v>-0.4366</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4129</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. BARBECHO GARCIA</t>
+          <t>G. SEVILLANO PUIG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1086</v>
+        <v>-0.9622000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4248</v>
+        <v>-2.3438</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3161</v>
+        <v>1.3815</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2231</v>
+        <v>1.7189</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4058</v>
+        <v>0.5386</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1827</v>
+        <v>1.1802</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3001</v>
+        <v>1.1194</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3402</v>
+        <v>0.5093</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0402</v>
+        <v>0.6101</v>
       </c>
       <c r="M11" t="n">
-        <v>0.077</v>
+        <v>0.5995</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.0293</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1425</v>
+        <v>0.5702</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1984</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1984</v>
+        <v>-3.3725</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3128</v>
+        <v>-1.2924</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0737</v>
+        <v>-0.0906</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2392</v>
+        <v>-1.2018</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. SEVILLANO PUIG</t>
+          <t>P. BARBECHO GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5574</v>
+        <v>-1.1749</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9389</v>
+        <v>-1.3227</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3815</v>
+        <v>0.1478</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7189</v>
+        <v>-1.2231</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5386</v>
+        <v>-1.4058</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1802</v>
+        <v>0.1827</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1194</v>
+        <v>-1.3001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5093</v>
+        <v>-1.3402</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6101</v>
+        <v>0.0402</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5995</v>
+        <v>0.077</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0293</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5702</v>
+        <v>0.1425</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.3725</v>
+        <v>-0.1984</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9838</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8876</v>
+        <v>0.2465</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6858</v>
+        <v>0.1757</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2018</v>
+        <v>0.0708</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.676100000000003</v>
+        <v>9.6112</v>
       </c>
       <c r="E13" t="n">
-        <v>5.509799999999998</v>
+        <v>6.4449</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1661</v>
+        <v>3.1664</v>
       </c>
       <c r="G13" t="n">
         <v>20.6442</v>
@@ -1456,7 +1456,7 @@
         <v>2.5638</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2274</v>
+        <v>0.2274000000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-6.943500000000001</v>
@@ -1468,13 +1468,13 @@
         <v>10.9112</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.4217</v>
+        <v>-3.4864</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5026</v>
+        <v>2.4378</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.924099999999999</v>
+        <v>-5.924300000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6032999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4625</v>
+        <v>2.7347</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2313</v>
+        <v>2.5171</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2312</v>
+        <v>0.2176</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2484</v>
@@ -1546,13 +1546,13 @@
         <v>2.9758</v>
       </c>
       <c r="S14" t="n">
-        <v>1.921</v>
+        <v>1.1932</v>
       </c>
       <c r="T14" t="n">
-        <v>1.746</v>
+        <v>1.0318</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1751</v>
+        <v>0.1615</v>
       </c>
       <c r="V14" t="n">
         <v>0.7979000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0792</v>
+        <v>1.0673</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3332</v>
+        <v>1.1292</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.254</v>
+        <v>-0.0618</v>
       </c>
       <c r="G15" t="n">
         <v>0.4798</v>
@@ -1624,13 +1624,13 @@
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6156</v>
+        <v>0.6037</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0204</v>
+        <v>0.8163</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4048</v>
+        <v>-0.2126</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2065</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5302</v>
+        <v>0.9646</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4728</v>
+        <v>1.5749</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9427</v>
+        <v>-0.6102</v>
       </c>
       <c r="G16" t="n">
         <v>-1.7166</v>
@@ -1702,13 +1702,13 @@
         <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7533</v>
+        <v>-0.3188</v>
       </c>
       <c r="T16" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.1701</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8213</v>
+        <v>-0.4889</v>
       </c>
       <c r="V16" t="n">
         <v>1.8097</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>J. BRADLEY MAYOL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5859</v>
+        <v>-0.2613</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5071</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9212</v>
+        <v>-0.8183</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3856</v>
+        <v>-1.779</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6577</v>
+        <v>0.0452</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2721</v>
+        <v>-1.8242</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.0003</v>
+        <v>0.1374</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.0003</v>
+        <v>0.3682</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.2308</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6146</v>
+        <v>-1.9165</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3425</v>
+        <v>-0.323</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2721</v>
+        <v>-1.5935</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2046</v>
+        <v>0.3274</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4932</v>
+        <v>0.4195</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2885</v>
+        <v>-0.0922</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4134</v>
+        <v>-0.7381</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0197</v>
+        <v>-1.7112</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6063</v>
+        <v>0.9731</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.272</v>
+        <v>-1.3856</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.4235</v>
+        <v>-1.6577</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8485</v>
+        <v>0.2721</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7475</v>
+        <v>-2.0003</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.9483</v>
+        <v>-2.0003</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2008</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.5245</v>
+        <v>0.6146</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.4752</v>
+        <v>0.3425</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0493</v>
+        <v>0.2721</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.579</v>
+        <v>0.5952</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.9596</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3806</v>
+        <v>0.5952</v>
       </c>
       <c r="S18" t="n">
-        <v>6.1716</v>
+        <v>0.0524</v>
       </c>
       <c r="T18" t="n">
-        <v>5.0959</v>
+        <v>0.2891</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0757</v>
+        <v>-0.2367</v>
       </c>
       <c r="V18" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BRADLEY MAYOL</t>
+          <t>M. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5018</v>
+        <v>-0.7511</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4633</v>
+        <v>0.1534</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0385</v>
+        <v>-0.9045</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.779</v>
+        <v>-2.0474</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0452</v>
+        <v>-2.923</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8242</v>
+        <v>0.8757</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1374</v>
+        <v>1.6901</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3682</v>
+        <v>-0.6494</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2308</v>
+        <v>2.3396</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9165</v>
+        <v>-3.7375</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.323</v>
+        <v>-2.2736</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5935</v>
+        <v>-1.4639</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1903</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>2.3806</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9131</v>
+        <v>0.2764</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6008</v>
+        <v>0.2325</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3124</v>
+        <v>0.0439</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.615</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. GARCIA CALVO</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6957</v>
+        <v>-1.1795</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4588</v>
+        <v>-0.5181</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2369</v>
+        <v>-0.6614</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0474</v>
+        <v>-2.0962</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.923</v>
+        <v>-0.9678</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8757</v>
+        <v>-1.1285</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6901</v>
+        <v>-0.9093</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6494</v>
+        <v>0.3682</v>
       </c>
       <c r="L20" t="n">
-        <v>2.3396</v>
+        <v>-1.2775</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.7375</v>
+        <v>-1.1869</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2736</v>
+        <v>-1.336</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4639</v>
+        <v>0.149</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3806</v>
+        <v>1.9838</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6682</v>
+        <v>0.7426</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3797</v>
+        <v>0.3912</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2885</v>
+        <v>0.3514</v>
       </c>
       <c r="V20" t="n">
-        <v>1.615</v>
+        <v>-1.8097</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.4085</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7135</v>
+        <v>-1.4608</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0282</v>
+        <v>1.1724</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6852</v>
+        <v>-2.6333</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0962</v>
+        <v>-2.0923</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9678</v>
+        <v>0.2566</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1285</v>
+        <v>-2.3489</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9093</v>
+        <v>-0.3119</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3682</v>
+        <v>0.4436</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2775</v>
+        <v>-0.7554</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1869</v>
+        <v>-1.7804</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.336</v>
+        <v>-0.187</v>
       </c>
       <c r="O21" t="n">
-        <v>0.149</v>
+        <v>-1.5935</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2086</v>
+        <v>-0.0864</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1189</v>
+        <v>0.2778</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3276</v>
+        <v>-0.3642</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8097</v>
+        <v>-0.8692</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8097</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4973</v>
+        <v>-3.0157</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3562</v>
+        <v>-3.0624</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8535</v>
+        <v>0.0467</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0923</v>
+        <v>-4.4866</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2566</v>
+        <v>-3.1599</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3489</v>
+        <v>-1.3267</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3119</v>
+        <v>-2.2292</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4436</v>
+        <v>-1.5567</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7554</v>
+        <v>-0.6725</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7804</v>
+        <v>-2.2573</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.187</v>
+        <v>-1.6032</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5935</v>
+        <v>-0.6542</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5871</v>
+        <v>2.3806</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1228</v>
+        <v>0.0822</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5384</v>
+        <v>0.1588</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5844</v>
+        <v>-0.0766</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3403</v>
+        <v>-4.629</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0826</v>
+        <v>-4.9785</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2577</v>
+        <v>0.3496</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4866</v>
+        <v>-5.272</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.1599</v>
+        <v>-4.4235</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3267</v>
+        <v>-0.8485</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2292</v>
+        <v>-1.7475</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5567</v>
+        <v>-1.9483</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6725</v>
+        <v>0.2008</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2573</v>
+        <v>-3.5245</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6032</v>
+        <v>-2.4752</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6542</v>
+        <v>-1.0493</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3887</v>
+        <v>-2.579</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9919</v>
+        <v>-4.9596</v>
       </c>
       <c r="R23" t="n">
         <v>2.3806</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2424</v>
+        <v>2.956</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8615</v>
+        <v>2.1371</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3809</v>
+        <v>0.819</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.676000000000002</v>
+        <v>-7.268899999999999</v>
       </c>
       <c r="E24" t="n">
         <v>-3.1662</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.5098</v>
+        <v>-4.1025</v>
       </c>
       <c r="G24" t="n">
         <v>-20.6443</v>
@@ -2296,7 +2296,7 @@
         <v>-11.1866</v>
       </c>
       <c r="I24" t="n">
-        <v>-9.457600000000001</v>
+        <v>-9.457599999999999</v>
       </c>
       <c r="J24" t="n">
         <v>-2.791500000000001</v>
@@ -2311,13 +2311,13 @@
         <v>-17.8529</v>
       </c>
       <c r="N24" t="n">
-        <v>-8.6229</v>
+        <v>-8.622900000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-9.2302</v>
       </c>
       <c r="P24" t="n">
-        <v>6.9434</v>
+        <v>6.943399999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-10.9111</v>
@@ -2326,13 +2326,13 @@
         <v>17.8546</v>
       </c>
       <c r="S24" t="n">
-        <v>4.4216</v>
+        <v>5.8287</v>
       </c>
       <c r="T24" t="n">
-        <v>5.924300000000001</v>
+        <v>5.924200000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5024</v>
+        <v>-0.09540000000000004</v>
       </c>
       <c r="V24" t="n">
         <v>0.6032000000000002</v>
@@ -2341,7 +2341,7 @@
         <v>4.6121</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.008900000000001</v>
+        <v>-4.0089</v>
       </c>
     </row>
   </sheetData>
